--- a/assets/resources/downloads/worksheets-roleplay-scorecard.xlsx
+++ b/assets/resources/downloads/worksheets-roleplay-scorecard.xlsx
@@ -8,11 +8,62 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+  </cellXfs>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Roleplay Scorecard</t>
         </is>
@@ -45,7 +96,7 @@
           <t xml:space="preserve">Summary</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A scorecard for rating a practice roleplay across clarity, relevance, listening, objection handling, and next step — so feedback is specific and you can track improvement over time.</t>
         </is>
@@ -71,7 +122,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rate a roleplay on five concrete skills</t>
         </is>
@@ -83,7 +134,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Give yourself one specific strength and one fix</t>
         </is>
@@ -95,7 +146,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Track scores across sessions</t>
         </is>
@@ -107,7 +158,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Choose a single focus for next time</t>
         </is>
@@ -133,7 +184,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">After a roleplay (with the AI Coach or a peer), rate each skill 1–5 and write one sentence of evidence. Pick exactly one thing to keep and one to change. Focus on one change per session.</t>
         </is>
@@ -159,7 +210,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Clarity 4 ("opener was tight"), Relevance 3 ("problem line was generic"), Listening 2 ("talked over the answer"), Objections 3, Next step 4. Keep: tight opener. Change next time: pause and let the prospect finish before responding.</t>
         </is>
@@ -185,7 +236,7 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Score to learn, not to judge yourself harshly. Use it on practice roleplays, not to critique real prospects. One honest fix per session beats a long list you cannot act on.</t>
         </is>
@@ -211,138 +262,143 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Skill</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Score (1-5)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Evidence / note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Clarity of opener</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Relevance to prospect</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Listening &amp; follow-up</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Objection handling</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Clear next step</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
